--- a/data/BXCC.xlsx
+++ b/data/BXCC.xlsx
@@ -6,27 +6,11 @@
     <workbookView activeTab="0" firstSheet="0" windowHeight="13125" windowWidth="13125" xWindow="0" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="B" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="X" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="BX" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="B" sheetId="4" state="visible" r:id="rId1"/>
+    <sheet name="X" sheetId="5" state="visible" r:id="rId2"/>
+    <sheet name="BX" sheetId="6" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="R_">'B'!$A$143:$AL$147</definedName>
-    <definedName localSheetId="0" name="U">'B'!$AO$83:$BD$120</definedName>
-    <definedName localSheetId="0" name="V">'B'!$A$124:$AL$139</definedName>
-    <definedName localSheetId="0" name="Y">'B'!$BG$83:$BI$120</definedName>
-    <definedName localSheetId="0" name="r_EIOU">'B'!$BG$1:$BV$38</definedName>
-    <definedName localSheetId="0" name="U_EIOU">'B'!$AO$1:$BD$38</definedName>
-    <definedName localSheetId="0" name="U_feed">'B'!$AO$42:$BD$79</definedName>
-    <definedName localSheetId="0" name="S_units">'B'!$A$1:$B$39</definedName>
-    <definedName localSheetId="1" name="R_">'X'!$A$163:$AE$183</definedName>
-    <definedName localSheetId="1" name="U">'X'!$AH$97:$BZ$141</definedName>
-    <definedName localSheetId="1" name="V">'X'!$A$145:$AE$159</definedName>
-    <definedName localSheetId="1" name="Y">'X'!$CC$97:$DU$141</definedName>
-    <definedName localSheetId="1" name="r_EIOU">'X'!$CC$1:$DU$45</definedName>
-    <definedName localSheetId="1" name="U_EIOU">'X'!$AH$1:$BZ$45</definedName>
-    <definedName localSheetId="1" name="U_feed">'X'!$AH$49:$BZ$93</definedName>
-    <definedName localSheetId="1" name="S_units">'X'!$A$1:$B$63</definedName>
     <definedName localSheetId="2" name="R_">'BX'!$A$235:$BL$259</definedName>
     <definedName localSheetId="2" name="U">'BX'!$BO$135:$CR$198</definedName>
     <definedName localSheetId="2" name="V">'BX'!$A$202:$BL$231</definedName>

--- a/data/BXCC.xlsx
+++ b/data/BXCC.xlsx
@@ -6,9 +6,9 @@
     <workbookView activeTab="0" firstSheet="0" windowHeight="13125" windowWidth="13125" xWindow="0" yWindow="0"/>
   </bookViews>
   <sheets>
-    <sheet name="B" sheetId="4" state="visible" r:id="rId1"/>
-    <sheet name="X" sheetId="5" state="visible" r:id="rId2"/>
-    <sheet name="BX" sheetId="6" state="visible" r:id="rId3"/>
+    <sheet name="B" sheetId="7" state="visible" r:id="rId1"/>
+    <sheet name="X" sheetId="8" state="visible" r:id="rId2"/>
+    <sheet name="BX" sheetId="9" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName localSheetId="2" name="R_">'BX'!$A$235:$BL$259</definedName>
@@ -14000,7 +14000,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="8">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="AL8" s="8">
         <v>0</v>
@@ -14039,7 +14039,7 @@
         <v>0</v>
       </c>
       <c r="AX8" s="8">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="AY8" s="8">
         <v>0</v>
@@ -14090,7 +14090,7 @@
         <v>0</v>
       </c>
       <c r="BO8" s="8">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="BP8" s="8">
         <v>0</v>
@@ -21665,7 +21665,7 @@
         <v>0</v>
       </c>
       <c r="AJ35" s="8">
-        <v>58054.842038054</v>
+        <v>58054.8420380546</v>
       </c>
       <c r="AK35" s="8">
         <v>0</v>
@@ -21802,7 +21802,7 @@
         <v>0</v>
       </c>
       <c r="CE35" s="8">
-        <v>0.72465121788954</v>
+        <v>0.724651217889545</v>
       </c>
       <c r="CF35" s="8">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="BO40" s="8">
-        <v>4306.09334056137</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="BP40" s="8">
         <v>0</v>
@@ -25062,7 +25062,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="8">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="AL50" s="8">
         <v>0</v>
@@ -25503,7 +25503,7 @@
         <v>0</v>
       </c>
       <c r="AK53" s="8">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="AL53" s="8">
         <v>0</v>
@@ -25884,7 +25884,7 @@
         <v>0</v>
       </c>
       <c r="BN55" s="8">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="BO55" s="8">
         <v>0</v>
@@ -26424,7 +26424,7 @@
         <v>0</v>
       </c>
       <c r="AX59" s="8">
-        <v>2511.39823520817</v>
+        <v>2511.39823520821</v>
       </c>
       <c r="AY59" s="8">
         <v>0</v>
@@ -27012,7 +27012,7 @@
         <v>0</v>
       </c>
       <c r="AX63" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AY63" s="8">
         <v>0</v>
@@ -27159,7 +27159,7 @@
         <v>0</v>
       </c>
       <c r="AY64" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AZ64" s="8">
         <v>0</v>
@@ -28386,7 +28386,7 @@
         <v>0</v>
       </c>
       <c r="AQ73" s="8">
-        <v>10407.5814017372</v>
+        <v>10407.5814017371</v>
       </c>
       <c r="AR73" s="8">
         <v>0</v>
@@ -28576,7 +28576,7 @@
         <v>0</v>
       </c>
       <c r="BH74" s="8">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="BI74" s="8">
         <v>0</v>
@@ -28875,7 +28875,7 @@
         <v>0</v>
       </c>
       <c r="BO76" s="8">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="BP76" s="8">
         <v>0</v>
@@ -29011,7 +29011,7 @@
         <v>0</v>
       </c>
       <c r="BN77" s="8">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="BO77" s="8">
         <v>0</v>
@@ -29147,7 +29147,7 @@
         <v>0</v>
       </c>
       <c r="BM78" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BN78" s="8">
         <v>0</v>
@@ -29247,7 +29247,7 @@
         <v>0</v>
       </c>
       <c r="AZ79" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="BA79" s="8">
         <v>0</v>
@@ -29755,7 +29755,7 @@
         <v>0</v>
       </c>
       <c r="AJ83" s="8">
-        <v>22059.3433863931</v>
+        <v>22059.3433863928</v>
       </c>
       <c r="AK83" s="8">
         <v>0</v>
@@ -29797,7 +29797,7 @@
         <v>0</v>
       </c>
       <c r="AX83" s="8">
-        <v>3204496.14876622</v>
+        <v>3204496.14876626</v>
       </c>
       <c r="AY83" s="8">
         <v>0</v>
@@ -29897,7 +29897,7 @@
         <v>0</v>
       </c>
       <c r="AK84" s="8">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="AL84" s="8">
         <v>0</v>
@@ -30153,7 +30153,7 @@
         <v>0</v>
       </c>
       <c r="BX85" s="8">
-        <v>21683.7905613496</v>
+        <v>21683.7905613501</v>
       </c>
       <c r="BY85" s="8">
         <v>0</v>
@@ -30214,7 +30214,7 @@
         <v>0</v>
       </c>
       <c r="AX86" s="8">
-        <v>5048.75518763039</v>
+        <v>5048.75518763036</v>
       </c>
       <c r="AY86" s="8">
         <v>0</v>
@@ -30362,7 +30362,7 @@
         <v>0</v>
       </c>
       <c r="BA87" s="8">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="BB87" s="8">
         <v>0</v>
@@ -30631,7 +30631,7 @@
         <v>0</v>
       </c>
       <c r="AX89" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AY89" s="8">
         <v>0</v>
@@ -30782,7 +30782,7 @@
         <v>0</v>
       </c>
       <c r="BB90" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BC90" s="8">
         <v>0</v>
@@ -31048,7 +31048,7 @@
         <v>0</v>
       </c>
       <c r="AX92" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="AY92" s="8">
         <v>0</v>
@@ -31202,7 +31202,7 @@
         <v>0</v>
       </c>
       <c r="BC93" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BD93" s="8">
         <v>0</v>
@@ -31733,7 +31733,7 @@
         <v>0</v>
       </c>
       <c r="AJ98" s="7">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="AK98" s="7">
         <v>0</v>
@@ -32561,7 +32561,7 @@
         <v>0</v>
       </c>
       <c r="AJ101" s="7">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="AK101" s="7">
         <v>0</v>
@@ -33143,7 +33143,7 @@
         <v>0</v>
       </c>
       <c r="AT103" s="7">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="AU103" s="7">
         <v>0</v>
@@ -33389,13 +33389,13 @@
         <v>0</v>
       </c>
       <c r="AJ104" s="7">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="AK104" s="7">
         <v>0</v>
       </c>
       <c r="AL104" s="7">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="AM104" s="7">
         <v>0</v>
@@ -33422,7 +33422,7 @@
         <v>0</v>
       </c>
       <c r="AU104" s="7">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="AV104" s="7">
         <v>0</v>
@@ -34223,7 +34223,7 @@
         <v>0</v>
       </c>
       <c r="AL107" s="7">
-        <v>2511.39823520817</v>
+        <v>2511.39823520821</v>
       </c>
       <c r="AM107" s="7">
         <v>0</v>
@@ -35327,7 +35327,7 @@
         <v>0</v>
       </c>
       <c r="AL111" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AM111" s="7">
         <v>0</v>
@@ -35606,7 +35606,7 @@
         <v>0</v>
       </c>
       <c r="AM112" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AN112" s="7">
         <v>0</v>
@@ -38084,7 +38084,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="7">
-        <v>10407.5814017372</v>
+        <v>10407.5814017371</v>
       </c>
       <c r="AL121" s="7">
         <v>0</v>
@@ -38381,7 +38381,7 @@
         <v>0</v>
       </c>
       <c r="AR122" s="7">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="AS122" s="7">
         <v>0</v>
@@ -38942,7 +38942,7 @@
         <v>0</v>
       </c>
       <c r="AU124" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="AV124" s="7">
         <v>0</v>
@@ -39215,7 +39215,7 @@
         <v>0</v>
       </c>
       <c r="AT125" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="AU125" s="7">
         <v>0</v>
@@ -39488,7 +39488,7 @@
         <v>0</v>
       </c>
       <c r="AS126" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AT126" s="7">
         <v>0</v>
@@ -39749,7 +39749,7 @@
         <v>0</v>
       </c>
       <c r="AN127" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AO127" s="7">
         <v>0</v>
@@ -40838,7 +40838,7 @@
         </is>
       </c>
       <c r="AI131" s="7">
-        <v>80114.185424447</v>
+        <v>80114.1854244474</v>
       </c>
       <c r="AJ131" s="7">
         <v>0</v>
@@ -40847,7 +40847,7 @@
         <v>0</v>
       </c>
       <c r="AL131" s="7">
-        <v>3204496.14876622</v>
+        <v>3204496.14876626</v>
       </c>
       <c r="AM131" s="7">
         <v>0</v>
@@ -41117,7 +41117,7 @@
         <v>0</v>
       </c>
       <c r="AJ132" s="7">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="AK132" s="7">
         <v>0</v>
@@ -41429,7 +41429,7 @@
         <v>0</v>
       </c>
       <c r="AV133" s="7">
-        <v>21683.7905613496</v>
+        <v>21683.7905613501</v>
       </c>
       <c r="AW133" s="7">
         <v>0</v>
@@ -41675,7 +41675,7 @@
         <v>0</v>
       </c>
       <c r="AL134" s="7">
-        <v>5048.75518763039</v>
+        <v>5048.75518763036</v>
       </c>
       <c r="AM134" s="7">
         <v>0</v>
@@ -41960,7 +41960,7 @@
         <v>0</v>
       </c>
       <c r="AO135" s="7">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="AP135" s="7">
         <v>0</v>
@@ -42254,7 +42254,7 @@
         <v>0</v>
       </c>
       <c r="AU136" s="7">
-        <v>4306.09334056137</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="AV136" s="7">
         <v>0</v>
@@ -42503,7 +42503,7 @@
         <v>0</v>
       </c>
       <c r="AL137" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AM137" s="7">
         <v>0</v>
@@ -42791,7 +42791,7 @@
         <v>0</v>
       </c>
       <c r="AP138" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AQ138" s="7">
         <v>0</v>
@@ -43331,7 +43331,7 @@
         <v>0</v>
       </c>
       <c r="AL140" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="AM140" s="7">
         <v>0</v>
@@ -43622,7 +43622,7 @@
         <v>0</v>
       </c>
       <c r="AQ141" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="AR141" s="7">
         <v>0</v>
@@ -44065,7 +44065,7 @@
         <v>0</v>
       </c>
       <c r="K146" s="7">
-        <v>37142.634115362</v>
+        <v>37142.6341153622</v>
       </c>
       <c r="L146" s="7">
         <v>0</v>
@@ -44104,7 +44104,7 @@
         <v>0</v>
       </c>
       <c r="X146" s="7">
-        <v>16030.3175923004</v>
+        <v>16030.3175923003</v>
       </c>
       <c r="Y146" s="7">
         <v>0</v>
@@ -44159,7 +44159,7 @@
         <v>0</v>
       </c>
       <c r="J147" s="7">
-        <v>5194.92773027326</v>
+        <v>5194.92773027576</v>
       </c>
       <c r="K147" s="7">
         <v>0</v>
@@ -44195,7 +44195,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="7">
-        <v>3202004.51890557</v>
+        <v>3202004.5189056</v>
       </c>
       <c r="W147" s="7">
         <v>0</v>
@@ -44253,7 +44253,7 @@
         <v>0</v>
       </c>
       <c r="I148" s="7">
-        <v>3162.49928465372</v>
+        <v>3162.49928465367</v>
       </c>
       <c r="J148" s="7">
         <v>0</v>
@@ -44298,7 +44298,7 @@
         <v>0</v>
       </c>
       <c r="X148" s="7">
-        <v>5653.47296904925</v>
+        <v>5653.47296904921</v>
       </c>
       <c r="Y148" s="7">
         <v>0</v>
@@ -44368,7 +44368,7 @@
         <v>0</v>
       </c>
       <c r="O149" s="7">
-        <v>813415.740060376</v>
+        <v>813415.740060384</v>
       </c>
       <c r="P149" s="7">
         <v>0</v>
@@ -44456,7 +44456,7 @@
         <v>0</v>
       </c>
       <c r="L150" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="M150" s="7">
         <v>0</v>
@@ -44577,7 +44577,7 @@
         <v>0</v>
       </c>
       <c r="T151" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="U151" s="7">
         <v>0</v>
@@ -44689,7 +44689,7 @@
         <v>0</v>
       </c>
       <c r="Y152" s="7">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="Z152" s="7">
         <v>0</v>
@@ -44795,7 +44795,7 @@
         <v>0</v>
       </c>
       <c r="AB153" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AC153" s="7">
         <v>0</v>
@@ -44898,7 +44898,7 @@
         <v>0</v>
       </c>
       <c r="AD154" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="AE154" s="7">
         <v>0</v>
@@ -44953,7 +44953,7 @@
         <v>0</v>
       </c>
       <c r="P155" s="7">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="Q155" s="7">
         <v>0</v>
@@ -45020,7 +45020,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="7">
-        <v>60946.5548992506</v>
+        <v>60946.5548992509</v>
       </c>
       <c r="G156" s="7">
         <v>0</v>
@@ -45111,7 +45111,7 @@
         <v>0</v>
       </c>
       <c r="D157" s="7">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="E157" s="7">
         <v>0</v>
@@ -45129,7 +45129,7 @@
         <v>0</v>
       </c>
       <c r="J157" s="7">
-        <v>0.000000000000101464011453041</v>
+        <v>0</v>
       </c>
       <c r="K157" s="7">
         <v>0</v>
@@ -45153,7 +45153,7 @@
         <v>0</v>
       </c>
       <c r="R157" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="S157" s="7">
         <v>0</v>
@@ -45220,13 +45220,13 @@
         <v>27606.4545189183</v>
       </c>
       <c r="H158" s="7">
-        <v>60240.4197442838</v>
+        <v>60240.4197442839</v>
       </c>
       <c r="I158" s="7">
         <v>0</v>
       </c>
       <c r="J158" s="7">
-        <v>6738.87888542647</v>
+        <v>6738.87888542642</v>
       </c>
       <c r="K158" s="7">
         <v>0</v>
@@ -45277,7 +45277,7 @@
         <v>0</v>
       </c>
       <c r="AA158" s="7">
-        <v>4306.09334056136</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="AB158" s="7">
         <v>0</v>
@@ -45317,7 +45317,7 @@
         <v>0</v>
       </c>
       <c r="H159" s="7">
-        <v>23202.8958695482</v>
+        <v>23202.8958695483</v>
       </c>
       <c r="I159" s="7">
         <v>0</v>
@@ -45664,7 +45664,7 @@
         <v>0</v>
       </c>
       <c r="F165" s="2">
-        <v>40734.7303283633</v>
+        <v>40734.7303283613</v>
       </c>
       <c r="G165" s="2">
         <v>0</v>
@@ -45764,7 +45764,7 @@
         <v>0</v>
       </c>
       <c r="G166" s="2">
-        <v>872.216637594378</v>
+        <v>872.216637594377</v>
       </c>
       <c r="H166" s="2">
         <v>0</v>
@@ -45864,7 +45864,7 @@
         <v>0</v>
       </c>
       <c r="H167" s="2">
-        <v>36781.3290129294</v>
+        <v>36781.3290129292</v>
       </c>
       <c r="I167" s="2">
         <v>0</v>
@@ -46206,7 +46206,7 @@
         <v>0</v>
       </c>
       <c r="Y170" s="2">
-        <v>24.966118677908</v>
+        <v>24.9661186779879</v>
       </c>
       <c r="Z170" s="2">
         <v>0</v>
@@ -46234,7 +46234,7 @@
         </is>
       </c>
       <c r="B171" s="2">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="C171" s="2">
         <v>0</v>
@@ -46334,7 +46334,7 @@
         <v>0</v>
       </c>
       <c r="C172" s="2">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="D172" s="2">
         <v>0</v>
@@ -46437,7 +46437,7 @@
         <v>0</v>
       </c>
       <c r="E173" s="2">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="F173" s="2">
         <v>0</v>
@@ -46558,7 +46558,7 @@
         <v>0</v>
       </c>
       <c r="M174" s="2">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="N174" s="2">
         <v>0</v>
@@ -46673,7 +46673,7 @@
         <v>0</v>
       </c>
       <c r="S175" s="2">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="T175" s="2">
         <v>0</v>
@@ -46764,7 +46764,7 @@
         <v>0</v>
       </c>
       <c r="Q176" s="2">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="R176" s="2">
         <v>0</v>
@@ -46873,7 +46873,7 @@
         <v>0</v>
       </c>
       <c r="U177" s="2">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="V177" s="2">
         <v>0</v>
@@ -46976,7 +46976,7 @@
         <v>0</v>
       </c>
       <c r="W178" s="2">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="X178" s="2">
         <v>0</v>
@@ -47082,7 +47082,7 @@
         <v>0</v>
       </c>
       <c r="Z179" s="2">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="AA179" s="2">
         <v>0</v>
@@ -47188,7 +47188,7 @@
         <v>0</v>
       </c>
       <c r="AC180" s="2">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="AD180" s="2">
         <v>0</v>
@@ -47291,7 +47291,7 @@
         <v>0</v>
       </c>
       <c r="AE181" s="2">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
     </row>
     <row r="182">
@@ -47316,7 +47316,7 @@
         <v>0</v>
       </c>
       <c r="G182" s="2">
-        <v>633.592333294874</v>
+        <v>633.592333294875</v>
       </c>
       <c r="H182" s="2">
         <v>0</v>
@@ -47361,7 +47361,7 @@
         <v>0</v>
       </c>
       <c r="V182" s="2">
-        <v>82605.8152851038</v>
+        <v>82605.8152850982</v>
       </c>
       <c r="W182" s="2">
         <v>0</v>
@@ -47404,7 +47404,7 @@
         <v>0</v>
       </c>
       <c r="D183" s="2">
-        <v>633.062840553138</v>
+        <v>633.062840553139</v>
       </c>
       <c r="E183" s="2">
         <v>0</v>
@@ -51535,7 +51535,7 @@
         <v>0</v>
       </c>
       <c r="BU21" s="8">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="BV21" s="8">
         <v>0</v>
@@ -51568,7 +51568,7 @@
         <v>0</v>
       </c>
       <c r="CF21" s="8">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="CG21" s="8">
         <v>0</v>
@@ -51598,7 +51598,7 @@
         <v>0</v>
       </c>
       <c r="CP21" s="8">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="CQ21" s="8">
         <v>0</v>
@@ -56770,7 +56770,7 @@
         <v>0</v>
       </c>
       <c r="BT48" s="8">
-        <v>58054.842038054</v>
+        <v>58054.8420380546</v>
       </c>
       <c r="BU48" s="8">
         <v>0</v>
@@ -56862,7 +56862,7 @@
         <v>0</v>
       </c>
       <c r="CZ48" s="8">
-        <v>0.72465121788954</v>
+        <v>0.724651217889545</v>
       </c>
       <c r="DA48" s="8">
         <v>0</v>
@@ -58388,7 +58388,7 @@
         <v>0</v>
       </c>
       <c r="CP56" s="8">
-        <v>4306.09334056137</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="CQ56" s="8">
         <v>0</v>
@@ -60368,7 +60368,7 @@
         <v>0</v>
       </c>
       <c r="BU70" s="8">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="BV70" s="8">
         <v>0</v>
@@ -61286,7 +61286,7 @@
         <v>0</v>
       </c>
       <c r="BU79" s="8">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="BV79" s="8">
         <v>0</v>
@@ -62033,7 +62033,7 @@
         <v>0</v>
       </c>
       <c r="CO86" s="8">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="CP86" s="8">
         <v>0</v>
@@ -62382,7 +62382,7 @@
         <v>0</v>
       </c>
       <c r="CF90" s="8">
-        <v>2511.39823520817</v>
+        <v>2511.39823520821</v>
       </c>
       <c r="CG90" s="8">
         <v>0</v>
@@ -62758,7 +62758,7 @@
         <v>0</v>
       </c>
       <c r="CF94" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="CG94" s="8">
         <v>0</v>
@@ -62855,7 +62855,7 @@
         <v>0</v>
       </c>
       <c r="CG95" s="8">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="CH95" s="8">
         <v>0</v>
@@ -64147,7 +64147,7 @@
         <v>10583778.8835768</v>
       </c>
       <c r="BY109" s="8">
-        <v>10407.5814017372</v>
+        <v>10407.5814017371</v>
       </c>
       <c r="BZ109" s="8">
         <v>0</v>
@@ -64283,7 +64283,7 @@
         <v>0</v>
       </c>
       <c r="CM110" s="8">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="CN110" s="8">
         <v>0</v>
@@ -64386,7 +64386,7 @@
         <v>0</v>
       </c>
       <c r="CP111" s="8">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="CQ111" s="8">
         <v>0</v>
@@ -64477,7 +64477,7 @@
         <v>0</v>
       </c>
       <c r="CO112" s="8">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="CP112" s="8">
         <v>0</v>
@@ -64568,7 +64568,7 @@
         <v>0</v>
       </c>
       <c r="CN113" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="CO113" s="8">
         <v>0</v>
@@ -64644,7 +64644,7 @@
         <v>0</v>
       </c>
       <c r="CH114" s="8">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="CI114" s="8">
         <v>0</v>
@@ -64696,7 +64696,7 @@
         <v>0</v>
       </c>
       <c r="BT115" s="8">
-        <v>22059.3433863931</v>
+        <v>22059.3433863928</v>
       </c>
       <c r="BU115" s="8">
         <v>0</v>
@@ -64732,7 +64732,7 @@
         <v>0</v>
       </c>
       <c r="CF115" s="8">
-        <v>3204496.14876622</v>
+        <v>3204496.14876626</v>
       </c>
       <c r="CG115" s="8">
         <v>0</v>
@@ -64793,7 +64793,7 @@
         <v>0</v>
       </c>
       <c r="BU116" s="8">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="BV116" s="8">
         <v>0</v>
@@ -64956,7 +64956,7 @@
         <v>0</v>
       </c>
       <c r="CR117" s="8">
-        <v>21683.7905613496</v>
+        <v>21683.7905613501</v>
       </c>
     </row>
     <row r="118">
@@ -65202,7 +65202,7 @@
         <v>0</v>
       </c>
       <c r="CF120" s="8">
-        <v>5048.75518763039</v>
+        <v>5048.75518763036</v>
       </c>
       <c r="CG120" s="8">
         <v>0</v>
@@ -65305,7 +65305,7 @@
         <v>0</v>
       </c>
       <c r="CI121" s="8">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="CJ121" s="8">
         <v>0</v>
@@ -65578,7 +65578,7 @@
         <v>0</v>
       </c>
       <c r="CF124" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="CG124" s="8">
         <v>0</v>
@@ -65684,7 +65684,7 @@
         <v>0</v>
       </c>
       <c r="CJ125" s="8">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="CK125" s="8">
         <v>0</v>
@@ -66048,7 +66048,7 @@
         <v>0</v>
       </c>
       <c r="CF129" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="CG129" s="8">
         <v>0</v>
@@ -66157,7 +66157,7 @@
         <v>0</v>
       </c>
       <c r="CK130" s="8">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="CL130" s="8">
         <v>0</v>
@@ -66566,7 +66566,7 @@
         <v>0</v>
       </c>
       <c r="BU137" s="7">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="BV137" s="7">
         <v>0</v>
@@ -67511,7 +67511,7 @@
         <v>0</v>
       </c>
       <c r="BU146" s="7">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="BV146" s="7">
         <v>0</v>
@@ -68306,7 +68306,7 @@
         <v>0</v>
       </c>
       <c r="CO153" s="7">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="CP153" s="7">
         <v>0</v>
@@ -68456,7 +68456,7 @@
         <v>0</v>
       </c>
       <c r="BU155" s="7">
-        <v>5820.73286270895</v>
+        <v>5820.73286270896</v>
       </c>
       <c r="BV155" s="7">
         <v>0</v>
@@ -68489,7 +68489,7 @@
         <v>2824.88564774492</v>
       </c>
       <c r="CF155" s="7">
-        <v>67354.0211167643</v>
+        <v>67354.0211167639</v>
       </c>
       <c r="CG155" s="7">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>0</v>
       </c>
       <c r="CP155" s="7">
-        <v>3155.64534081532</v>
+        <v>3155.64534081533</v>
       </c>
       <c r="CQ155" s="7">
         <v>0</v>
@@ -68699,7 +68699,7 @@
         <v>0</v>
       </c>
       <c r="CF157" s="7">
-        <v>2511.39823520817</v>
+        <v>2511.39823520821</v>
       </c>
       <c r="CG157" s="7">
         <v>0</v>
@@ -69119,7 +69119,7 @@
         <v>0</v>
       </c>
       <c r="CF161" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="CG161" s="7">
         <v>0</v>
@@ -69227,7 +69227,7 @@
         <v>0</v>
       </c>
       <c r="CG162" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="CH162" s="7">
         <v>0</v>
@@ -70673,7 +70673,7 @@
         <v>10583778.8835768</v>
       </c>
       <c r="BY176" s="7">
-        <v>10407.5814017372</v>
+        <v>10407.5814017371</v>
       </c>
       <c r="BZ176" s="7">
         <v>0</v>
@@ -70820,7 +70820,7 @@
         <v>0</v>
       </c>
       <c r="CM177" s="7">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="CN177" s="7">
         <v>0</v>
@@ -70934,7 +70934,7 @@
         <v>0</v>
       </c>
       <c r="CP178" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="CQ178" s="7">
         <v>0</v>
@@ -71036,7 +71036,7 @@
         <v>0</v>
       </c>
       <c r="CO179" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="CP179" s="7">
         <v>0</v>
@@ -71138,7 +71138,7 @@
         <v>0</v>
       </c>
       <c r="CN180" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="CO180" s="7">
         <v>0</v>
@@ -71225,7 +71225,7 @@
         <v>0</v>
       </c>
       <c r="CH181" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="CI181" s="7">
         <v>0</v>
@@ -71288,7 +71288,7 @@
         <v>0</v>
       </c>
       <c r="BT182" s="7">
-        <v>80114.185424447</v>
+        <v>80114.1854244474</v>
       </c>
       <c r="BU182" s="7">
         <v>0</v>
@@ -71324,7 +71324,7 @@
         <v>0</v>
       </c>
       <c r="CF182" s="7">
-        <v>3204496.14876622</v>
+        <v>3204496.14876626</v>
       </c>
       <c r="CG182" s="7">
         <v>0</v>
@@ -71396,7 +71396,7 @@
         <v>0</v>
       </c>
       <c r="BU183" s="7">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="BV183" s="7">
         <v>0</v>
@@ -71570,7 +71570,7 @@
         <v>0</v>
       </c>
       <c r="CR184" s="7">
-        <v>21683.7905613496</v>
+        <v>21683.7905613501</v>
       </c>
       <c r="CU184" s="3" t="inlineStr">
         <is>
@@ -71849,7 +71849,7 @@
         <v>0</v>
       </c>
       <c r="CF187" s="7">
-        <v>5048.75518763039</v>
+        <v>5048.75518763036</v>
       </c>
       <c r="CG187" s="7">
         <v>0</v>
@@ -71963,7 +71963,7 @@
         <v>0</v>
       </c>
       <c r="CI188" s="7">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="CJ188" s="7">
         <v>0</v>
@@ -72194,7 +72194,7 @@
         <v>0</v>
       </c>
       <c r="CP190" s="7">
-        <v>4306.09334056137</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="CQ190" s="7">
         <v>0</v>
@@ -72269,7 +72269,7 @@
         <v>0</v>
       </c>
       <c r="CF191" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="CG191" s="7">
         <v>0</v>
@@ -72386,7 +72386,7 @@
         <v>0</v>
       </c>
       <c r="CJ192" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="CK192" s="7">
         <v>0</v>
@@ -72794,7 +72794,7 @@
         <v>0</v>
       </c>
       <c r="CF196" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="CG196" s="7">
         <v>0</v>
@@ -72914,7 +72914,7 @@
         <v>0</v>
       </c>
       <c r="CK197" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="CL197" s="7">
         <v>0</v>
@@ -74246,7 +74246,7 @@
         <v>0</v>
       </c>
       <c r="Z207" s="7">
-        <v>37142.634115362</v>
+        <v>37142.6341153622</v>
       </c>
       <c r="AA207" s="7">
         <v>0</v>
@@ -74318,7 +74318,7 @@
         <v>0</v>
       </c>
       <c r="AX207" s="7">
-        <v>16030.3175923004</v>
+        <v>16030.3175923003</v>
       </c>
       <c r="AY207" s="7">
         <v>0</v>
@@ -74439,7 +74439,7 @@
         <v>0</v>
       </c>
       <c r="Y208" s="7">
-        <v>5194.92773027326</v>
+        <v>5194.92773027576</v>
       </c>
       <c r="Z208" s="7">
         <v>0</v>
@@ -74508,7 +74508,7 @@
         <v>0</v>
       </c>
       <c r="AV208" s="7">
-        <v>3202004.51890557</v>
+        <v>3202004.5189056</v>
       </c>
       <c r="AW208" s="7">
         <v>0</v>
@@ -75220,7 +75220,7 @@
         <v>0</v>
       </c>
       <c r="X212" s="7">
-        <v>3162.49928465372</v>
+        <v>3162.49928465367</v>
       </c>
       <c r="Y212" s="7">
         <v>0</v>
@@ -75298,7 +75298,7 @@
         <v>0</v>
       </c>
       <c r="AX212" s="7">
-        <v>5653.47296904925</v>
+        <v>5653.47296904921</v>
       </c>
       <c r="AY212" s="7">
         <v>0</v>
@@ -76643,7 +76643,7 @@
         <v>0</v>
       </c>
       <c r="AO219" s="7">
-        <v>813415.740060376</v>
+        <v>813415.740060384</v>
       </c>
       <c r="AP219" s="7">
         <v>0</v>
@@ -76797,7 +76797,7 @@
         <v>0</v>
       </c>
       <c r="AA220" s="7">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AB220" s="7">
         <v>0</v>
@@ -77050,7 +77050,7 @@
         <v>0</v>
       </c>
       <c r="AT221" s="7">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AU221" s="7">
         <v>0</v>
@@ -77267,7 +77267,7 @@
         <v>0</v>
       </c>
       <c r="BA222" s="7">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="BB222" s="7">
         <v>0</v>
@@ -77475,7 +77475,7 @@
         <v>0</v>
       </c>
       <c r="BE223" s="7">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BF223" s="7">
         <v>0</v>
@@ -77686,7 +77686,7 @@
         <v>0</v>
       </c>
       <c r="BJ224" s="7">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BK224" s="7">
         <v>0</v>
@@ -78018,7 +78018,7 @@
         <v>0</v>
       </c>
       <c r="AP226" s="7">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="AQ226" s="7">
         <v>0</v>
@@ -78151,7 +78151,7 @@
         <v>0</v>
       </c>
       <c r="U227" s="7">
-        <v>60946.5548992506</v>
+        <v>60946.5548992509</v>
       </c>
       <c r="V227" s="7">
         <v>0</v>
@@ -78338,7 +78338,7 @@
         <v>0</v>
       </c>
       <c r="R228" s="7">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="S228" s="7">
         <v>0</v>
@@ -78359,7 +78359,7 @@
         <v>0</v>
       </c>
       <c r="Y228" s="7">
-        <v>0.000000000000101464011453041</v>
+        <v>0</v>
       </c>
       <c r="Z228" s="7">
         <v>0</v>
@@ -78416,7 +78416,7 @@
         <v>0</v>
       </c>
       <c r="AR228" s="7">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="AS228" s="7">
         <v>0</v>
@@ -78549,13 +78549,13 @@
         <v>27606.4545189183</v>
       </c>
       <c r="W229" s="7">
-        <v>60240.4197442838</v>
+        <v>60240.4197442839</v>
       </c>
       <c r="X229" s="7">
         <v>0</v>
       </c>
       <c r="Y229" s="7">
-        <v>6738.87888542647</v>
+        <v>6738.87888542642</v>
       </c>
       <c r="Z229" s="7">
         <v>0</v>
@@ -78648,7 +78648,7 @@
         <v>0</v>
       </c>
       <c r="BD229" s="7">
-        <v>4306.09334056136</v>
+        <v>4306.09334056135</v>
       </c>
       <c r="BE229" s="7">
         <v>0</v>
@@ -78941,7 +78941,7 @@
         <v>0</v>
       </c>
       <c r="W231" s="7">
-        <v>23202.8958695482</v>
+        <v>23202.8958695483</v>
       </c>
       <c r="X231" s="7">
         <v>0</v>
@@ -79651,7 +79651,7 @@
         <v>0</v>
       </c>
       <c r="U237" s="2">
-        <v>40734.7303283633</v>
+        <v>40734.7303283613</v>
       </c>
       <c r="V237" s="2">
         <v>0</v>
@@ -79850,7 +79850,7 @@
         <v>0</v>
       </c>
       <c r="V238" s="2">
-        <v>872.216637594378</v>
+        <v>872.216637594377</v>
       </c>
       <c r="W238" s="2">
         <v>0</v>
@@ -80049,7 +80049,7 @@
         <v>0</v>
       </c>
       <c r="W239" s="2">
-        <v>36781.3290129294</v>
+        <v>36781.3290129292</v>
       </c>
       <c r="X239" s="2">
         <v>0</v>
@@ -80727,7 +80727,7 @@
         <v>0</v>
       </c>
       <c r="BA242" s="2">
-        <v>24.966118677908</v>
+        <v>24.9661186779879</v>
       </c>
       <c r="BB242" s="2">
         <v>0</v>
@@ -80773,7 +80773,7 @@
         <v>0</v>
       </c>
       <c r="C243" s="2">
-        <v>45017.5962724527</v>
+        <v>45017.5962724529</v>
       </c>
       <c r="D243" s="2">
         <v>0</v>
@@ -81192,7 +81192,7 @@
         <v>0</v>
       </c>
       <c r="L245" s="2">
-        <v>66251.1826186745</v>
+        <v>66251.1826186753</v>
       </c>
       <c r="M245" s="2">
         <v>0</v>
@@ -81605,7 +81605,7 @@
         <v>0</v>
       </c>
       <c r="S247" s="2">
-        <v>290.153801920188</v>
+        <v>290.153801920193</v>
       </c>
       <c r="T247" s="2">
         <v>0</v>
@@ -81828,7 +81828,7 @@
         <v>0</v>
       </c>
       <c r="AB248" s="2">
-        <v>4830.44426252758</v>
+        <v>4830.44426252755</v>
       </c>
       <c r="AC248" s="2">
         <v>0</v>
@@ -82467,7 +82467,7 @@
         <v>0</v>
       </c>
       <c r="AS251" s="2">
-        <v>668.843689185036</v>
+        <v>668.84368918504</v>
       </c>
       <c r="AT251" s="2">
         <v>0</v>
@@ -82657,7 +82657,7 @@
         <v>0</v>
       </c>
       <c r="AQ252" s="2">
-        <v>3749358.38011217</v>
+        <v>3749358.38011219</v>
       </c>
       <c r="AR252" s="2">
         <v>0</v>
@@ -82865,7 +82865,7 @@
         <v>0</v>
       </c>
       <c r="AU253" s="2">
-        <v>184686.529997729</v>
+        <v>184686.529997727</v>
       </c>
       <c r="AV253" s="2">
         <v>0</v>
@@ -83067,7 +83067,7 @@
         <v>0</v>
       </c>
       <c r="AW254" s="2">
-        <v>3090735.74001444</v>
+        <v>3090735.74001448</v>
       </c>
       <c r="AX254" s="2">
         <v>0</v>
@@ -83278,7 +83278,7 @@
         <v>0</v>
       </c>
       <c r="BB255" s="2">
-        <v>5023.78906895248</v>
+        <v>5023.78906895237</v>
       </c>
       <c r="BC255" s="2">
         <v>0</v>
@@ -83486,7 +83486,7 @@
         <v>0</v>
       </c>
       <c r="BF256" s="2">
-        <v>82.0916287907192</v>
+        <v>82.0916287907193</v>
       </c>
       <c r="BG256" s="2">
         <v>0</v>
@@ -83697,7 +83697,7 @@
         <v>0</v>
       </c>
       <c r="BK257" s="2">
-        <v>43.206120416168</v>
+        <v>43.2061204161677</v>
       </c>
       <c r="BL257" s="2">
         <v>0</v>
@@ -83770,7 +83770,7 @@
         <v>0</v>
       </c>
       <c r="V258" s="2">
-        <v>633.592333294874</v>
+        <v>633.592333294875</v>
       </c>
       <c r="W258" s="2">
         <v>0</v>
@@ -83848,7 +83848,7 @@
         <v>0</v>
       </c>
       <c r="AV258" s="2">
-        <v>82605.8152851038</v>
+        <v>82605.8152850982</v>
       </c>
       <c r="AW258" s="2">
         <v>0</v>
@@ -83954,7 +83954,7 @@
         <v>0</v>
       </c>
       <c r="R259" s="2">
-        <v>633.062840553138</v>
+        <v>633.062840553139</v>
       </c>
       <c r="S259" s="2">
         <v>0</v>

--- a/data/BXCC.xlsx
+++ b/data/BXCC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mkh2/github/MaterialExergyPaper2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365003F7-D8A3-674B-93B7-76FF7EE39DBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAAF5769-3C4B-9C4F-9E17-5EB86F6BA5DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="22820" windowHeight="20800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="B" sheetId="16" r:id="rId1"/>
@@ -619,10 +619,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -642,6 +638,10 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4928,43 +4928,43 @@
       </c>
     </row>
     <row r="39" spans="1:74" x14ac:dyDescent="0.2">
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="AP39" s="8" t="s">
+      <c r="AP39" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AQ39" s="9"/>
-      <c r="AR39" s="9"/>
-      <c r="AS39" s="9"/>
-      <c r="AT39" s="9"/>
-      <c r="AU39" s="9"/>
-      <c r="AV39" s="9"/>
-      <c r="AW39" s="9"/>
-      <c r="AX39" s="9"/>
-      <c r="AY39" s="9"/>
-      <c r="AZ39" s="9"/>
-      <c r="BA39" s="9"/>
-      <c r="BB39" s="9"/>
-      <c r="BC39" s="9"/>
-      <c r="BD39" s="9"/>
-      <c r="BH39" s="8" t="s">
+      <c r="AQ39" s="16"/>
+      <c r="AR39" s="16"/>
+      <c r="AS39" s="16"/>
+      <c r="AT39" s="16"/>
+      <c r="AU39" s="16"/>
+      <c r="AV39" s="16"/>
+      <c r="AW39" s="16"/>
+      <c r="AX39" s="16"/>
+      <c r="AY39" s="16"/>
+      <c r="AZ39" s="16"/>
+      <c r="BA39" s="16"/>
+      <c r="BB39" s="16"/>
+      <c r="BC39" s="16"/>
+      <c r="BD39" s="16"/>
+      <c r="BH39" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="BI39" s="9"/>
-      <c r="BJ39" s="9"/>
-      <c r="BK39" s="9"/>
-      <c r="BL39" s="9"/>
-      <c r="BM39" s="9"/>
-      <c r="BN39" s="9"/>
-      <c r="BO39" s="9"/>
-      <c r="BP39" s="9"/>
-      <c r="BQ39" s="9"/>
-      <c r="BR39" s="9"/>
-      <c r="BS39" s="9"/>
-      <c r="BT39" s="9"/>
-      <c r="BU39" s="9"/>
-      <c r="BV39" s="9"/>
+      <c r="BI39" s="16"/>
+      <c r="BJ39" s="16"/>
+      <c r="BK39" s="16"/>
+      <c r="BL39" s="16"/>
+      <c r="BM39" s="16"/>
+      <c r="BN39" s="16"/>
+      <c r="BO39" s="16"/>
+      <c r="BP39" s="16"/>
+      <c r="BQ39" s="16"/>
+      <c r="BR39" s="16"/>
+      <c r="BS39" s="16"/>
+      <c r="BT39" s="16"/>
+      <c r="BU39" s="16"/>
+      <c r="BV39" s="16"/>
     </row>
     <row r="42" spans="1:74" ht="112" x14ac:dyDescent="0.2">
       <c r="AP42" s="3" t="s">
@@ -6864,23 +6864,23 @@
       </c>
     </row>
     <row r="80" spans="41:56" x14ac:dyDescent="0.2">
-      <c r="AP80" s="8" t="s">
+      <c r="AP80" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AQ80" s="9"/>
-      <c r="AR80" s="9"/>
-      <c r="AS80" s="9"/>
-      <c r="AT80" s="9"/>
-      <c r="AU80" s="9"/>
-      <c r="AV80" s="9"/>
-      <c r="AW80" s="9"/>
-      <c r="AX80" s="9"/>
-      <c r="AY80" s="9"/>
-      <c r="AZ80" s="9"/>
-      <c r="BA80" s="9"/>
-      <c r="BB80" s="9"/>
-      <c r="BC80" s="9"/>
-      <c r="BD80" s="9"/>
+      <c r="AQ80" s="16"/>
+      <c r="AR80" s="16"/>
+      <c r="AS80" s="16"/>
+      <c r="AT80" s="16"/>
+      <c r="AU80" s="16"/>
+      <c r="AV80" s="16"/>
+      <c r="AW80" s="16"/>
+      <c r="AX80" s="16"/>
+      <c r="AY80" s="16"/>
+      <c r="AZ80" s="16"/>
+      <c r="BA80" s="16"/>
+      <c r="BB80" s="16"/>
+      <c r="BC80" s="16"/>
+      <c r="BD80" s="16"/>
     </row>
     <row r="83" spans="41:61" ht="112" x14ac:dyDescent="0.2">
       <c r="AP83" s="3" t="s">
@@ -9119,27 +9119,27 @@
       </c>
     </row>
     <row r="121" spans="1:61" x14ac:dyDescent="0.2">
-      <c r="AP121" s="8" t="s">
+      <c r="AP121" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AQ121" s="9"/>
-      <c r="AR121" s="9"/>
-      <c r="AS121" s="9"/>
-      <c r="AT121" s="9"/>
-      <c r="AU121" s="9"/>
-      <c r="AV121" s="9"/>
-      <c r="AW121" s="9"/>
-      <c r="AX121" s="9"/>
-      <c r="AY121" s="9"/>
-      <c r="AZ121" s="9"/>
-      <c r="BA121" s="9"/>
-      <c r="BB121" s="9"/>
-      <c r="BC121" s="9"/>
-      <c r="BD121" s="9"/>
-      <c r="BH121" s="8" t="s">
+      <c r="AQ121" s="16"/>
+      <c r="AR121" s="16"/>
+      <c r="AS121" s="16"/>
+      <c r="AT121" s="16"/>
+      <c r="AU121" s="16"/>
+      <c r="AV121" s="16"/>
+      <c r="AW121" s="16"/>
+      <c r="AX121" s="16"/>
+      <c r="AY121" s="16"/>
+      <c r="AZ121" s="16"/>
+      <c r="BA121" s="16"/>
+      <c r="BB121" s="16"/>
+      <c r="BC121" s="16"/>
+      <c r="BD121" s="16"/>
+      <c r="BH121" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="BI121" s="9"/>
+      <c r="BI121" s="16"/>
     </row>
     <row r="124" spans="1:61" ht="236" x14ac:dyDescent="0.2">
       <c r="B124" s="3" t="s">
@@ -10995,45 +10995,45 @@
       </c>
     </row>
     <row r="140" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B140" s="8" t="s">
+      <c r="B140" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C140" s="9"/>
-      <c r="D140" s="9"/>
-      <c r="E140" s="9"/>
-      <c r="F140" s="9"/>
-      <c r="G140" s="9"/>
-      <c r="H140" s="9"/>
-      <c r="I140" s="9"/>
-      <c r="J140" s="9"/>
-      <c r="K140" s="9"/>
-      <c r="L140" s="9"/>
-      <c r="M140" s="9"/>
-      <c r="N140" s="9"/>
-      <c r="O140" s="9"/>
-      <c r="P140" s="9"/>
-      <c r="Q140" s="9"/>
-      <c r="R140" s="9"/>
-      <c r="S140" s="9"/>
-      <c r="T140" s="9"/>
-      <c r="U140" s="9"/>
-      <c r="V140" s="9"/>
-      <c r="W140" s="9"/>
-      <c r="X140" s="9"/>
-      <c r="Y140" s="9"/>
-      <c r="Z140" s="9"/>
-      <c r="AA140" s="9"/>
-      <c r="AB140" s="9"/>
-      <c r="AC140" s="9"/>
-      <c r="AD140" s="9"/>
-      <c r="AE140" s="9"/>
-      <c r="AF140" s="9"/>
-      <c r="AG140" s="9"/>
-      <c r="AH140" s="9"/>
-      <c r="AI140" s="9"/>
-      <c r="AJ140" s="9"/>
-      <c r="AK140" s="9"/>
-      <c r="AL140" s="9"/>
+      <c r="C140" s="16"/>
+      <c r="D140" s="16"/>
+      <c r="E140" s="16"/>
+      <c r="F140" s="16"/>
+      <c r="G140" s="16"/>
+      <c r="H140" s="16"/>
+      <c r="I140" s="16"/>
+      <c r="J140" s="16"/>
+      <c r="K140" s="16"/>
+      <c r="L140" s="16"/>
+      <c r="M140" s="16"/>
+      <c r="N140" s="16"/>
+      <c r="O140" s="16"/>
+      <c r="P140" s="16"/>
+      <c r="Q140" s="16"/>
+      <c r="R140" s="16"/>
+      <c r="S140" s="16"/>
+      <c r="T140" s="16"/>
+      <c r="U140" s="16"/>
+      <c r="V140" s="16"/>
+      <c r="W140" s="16"/>
+      <c r="X140" s="16"/>
+      <c r="Y140" s="16"/>
+      <c r="Z140" s="16"/>
+      <c r="AA140" s="16"/>
+      <c r="AB140" s="16"/>
+      <c r="AC140" s="16"/>
+      <c r="AD140" s="16"/>
+      <c r="AE140" s="16"/>
+      <c r="AF140" s="16"/>
+      <c r="AG140" s="16"/>
+      <c r="AH140" s="16"/>
+      <c r="AI140" s="16"/>
+      <c r="AJ140" s="16"/>
+      <c r="AK140" s="16"/>
+      <c r="AL140" s="16"/>
     </row>
     <row r="143" spans="1:38" ht="236" x14ac:dyDescent="0.2">
       <c r="B143" s="3" t="s">
@@ -11613,45 +11613,45 @@
       </c>
     </row>
     <row r="148" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C148" s="9"/>
-      <c r="D148" s="9"/>
-      <c r="E148" s="9"/>
-      <c r="F148" s="9"/>
-      <c r="G148" s="9"/>
-      <c r="H148" s="9"/>
-      <c r="I148" s="9"/>
-      <c r="J148" s="9"/>
-      <c r="K148" s="9"/>
-      <c r="L148" s="9"/>
-      <c r="M148" s="9"/>
-      <c r="N148" s="9"/>
-      <c r="O148" s="9"/>
-      <c r="P148" s="9"/>
-      <c r="Q148" s="9"/>
-      <c r="R148" s="9"/>
-      <c r="S148" s="9"/>
-      <c r="T148" s="9"/>
-      <c r="U148" s="9"/>
-      <c r="V148" s="9"/>
-      <c r="W148" s="9"/>
-      <c r="X148" s="9"/>
-      <c r="Y148" s="9"/>
-      <c r="Z148" s="9"/>
-      <c r="AA148" s="9"/>
-      <c r="AB148" s="9"/>
-      <c r="AC148" s="9"/>
-      <c r="AD148" s="9"/>
-      <c r="AE148" s="9"/>
-      <c r="AF148" s="9"/>
-      <c r="AG148" s="9"/>
-      <c r="AH148" s="9"/>
-      <c r="AI148" s="9"/>
-      <c r="AJ148" s="9"/>
-      <c r="AK148" s="9"/>
-      <c r="AL148" s="9"/>
+      <c r="C148" s="16"/>
+      <c r="D148" s="16"/>
+      <c r="E148" s="16"/>
+      <c r="F148" s="16"/>
+      <c r="G148" s="16"/>
+      <c r="H148" s="16"/>
+      <c r="I148" s="16"/>
+      <c r="J148" s="16"/>
+      <c r="K148" s="16"/>
+      <c r="L148" s="16"/>
+      <c r="M148" s="16"/>
+      <c r="N148" s="16"/>
+      <c r="O148" s="16"/>
+      <c r="P148" s="16"/>
+      <c r="Q148" s="16"/>
+      <c r="R148" s="16"/>
+      <c r="S148" s="16"/>
+      <c r="T148" s="16"/>
+      <c r="U148" s="16"/>
+      <c r="V148" s="16"/>
+      <c r="W148" s="16"/>
+      <c r="X148" s="16"/>
+      <c r="Y148" s="16"/>
+      <c r="Z148" s="16"/>
+      <c r="AA148" s="16"/>
+      <c r="AB148" s="16"/>
+      <c r="AC148" s="16"/>
+      <c r="AD148" s="16"/>
+      <c r="AE148" s="16"/>
+      <c r="AF148" s="16"/>
+      <c r="AG148" s="16"/>
+      <c r="AH148" s="16"/>
+      <c r="AI148" s="16"/>
+      <c r="AJ148" s="16"/>
+      <c r="AK148" s="16"/>
+      <c r="AL148" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -14716,38 +14716,38 @@
       <c r="B32" s="5">
         <v>1</v>
       </c>
-      <c r="AI32" s="8" t="s">
+      <c r="AI32" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="AJ32" s="9"/>
-      <c r="AK32" s="9"/>
-      <c r="AL32" s="9"/>
-      <c r="AM32" s="9"/>
-      <c r="AN32" s="9"/>
-      <c r="AO32" s="9"/>
-      <c r="AP32" s="9"/>
-      <c r="AQ32" s="9"/>
-      <c r="AR32" s="9"/>
-      <c r="AS32" s="9"/>
-      <c r="AT32" s="9"/>
-      <c r="AU32" s="9"/>
-      <c r="AV32" s="9"/>
-      <c r="AZ32" s="8" t="s">
+      <c r="AJ32" s="16"/>
+      <c r="AK32" s="16"/>
+      <c r="AL32" s="16"/>
+      <c r="AM32" s="16"/>
+      <c r="AN32" s="16"/>
+      <c r="AO32" s="16"/>
+      <c r="AP32" s="16"/>
+      <c r="AQ32" s="16"/>
+      <c r="AR32" s="16"/>
+      <c r="AS32" s="16"/>
+      <c r="AT32" s="16"/>
+      <c r="AU32" s="16"/>
+      <c r="AV32" s="16"/>
+      <c r="AZ32" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="BA32" s="9"/>
-      <c r="BB32" s="9"/>
-      <c r="BC32" s="9"/>
-      <c r="BD32" s="9"/>
-      <c r="BE32" s="9"/>
-      <c r="BF32" s="9"/>
-      <c r="BG32" s="9"/>
-      <c r="BH32" s="9"/>
-      <c r="BI32" s="9"/>
-      <c r="BJ32" s="9"/>
-      <c r="BK32" s="9"/>
-      <c r="BL32" s="9"/>
-      <c r="BM32" s="9"/>
+      <c r="BA32" s="16"/>
+      <c r="BB32" s="16"/>
+      <c r="BC32" s="16"/>
+      <c r="BD32" s="16"/>
+      <c r="BE32" s="16"/>
+      <c r="BF32" s="16"/>
+      <c r="BG32" s="16"/>
+      <c r="BH32" s="16"/>
+      <c r="BI32" s="16"/>
+      <c r="BJ32" s="16"/>
+      <c r="BK32" s="16"/>
+      <c r="BL32" s="16"/>
+      <c r="BM32" s="16"/>
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
@@ -15558,7 +15558,7 @@
       </c>
     </row>
     <row r="50" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="15" t="s">
         <v>53</v>
       </c>
       <c r="AH50" s="2" t="s">
@@ -16313,22 +16313,22 @@
       </c>
     </row>
     <row r="66" spans="34:52" x14ac:dyDescent="0.2">
-      <c r="AI66" s="8" t="s">
+      <c r="AI66" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="AJ66" s="9"/>
-      <c r="AK66" s="9"/>
-      <c r="AL66" s="9"/>
-      <c r="AM66" s="9"/>
-      <c r="AN66" s="9"/>
-      <c r="AO66" s="9"/>
-      <c r="AP66" s="9"/>
-      <c r="AQ66" s="9"/>
-      <c r="AR66" s="9"/>
-      <c r="AS66" s="9"/>
-      <c r="AT66" s="9"/>
-      <c r="AU66" s="9"/>
-      <c r="AV66" s="9"/>
+      <c r="AJ66" s="16"/>
+      <c r="AK66" s="16"/>
+      <c r="AL66" s="16"/>
+      <c r="AM66" s="16"/>
+      <c r="AN66" s="16"/>
+      <c r="AO66" s="16"/>
+      <c r="AP66" s="16"/>
+      <c r="AQ66" s="16"/>
+      <c r="AR66" s="16"/>
+      <c r="AS66" s="16"/>
+      <c r="AT66" s="16"/>
+      <c r="AU66" s="16"/>
+      <c r="AV66" s="16"/>
     </row>
     <row r="69" spans="34:52" ht="179" x14ac:dyDescent="0.2">
       <c r="AI69" s="3" t="s">
@@ -17968,23 +17968,23 @@
       </c>
     </row>
     <row r="100" spans="1:52" x14ac:dyDescent="0.2">
-      <c r="AI100" s="8" t="s">
+      <c r="AI100" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="AJ100" s="9"/>
-      <c r="AK100" s="9"/>
-      <c r="AL100" s="9"/>
-      <c r="AM100" s="9"/>
-      <c r="AN100" s="9"/>
-      <c r="AO100" s="9"/>
-      <c r="AP100" s="9"/>
-      <c r="AQ100" s="9"/>
-      <c r="AR100" s="9"/>
-      <c r="AS100" s="9"/>
-      <c r="AT100" s="9"/>
-      <c r="AU100" s="9"/>
-      <c r="AV100" s="9"/>
-      <c r="AZ100" s="8" t="s">
+      <c r="AJ100" s="16"/>
+      <c r="AK100" s="16"/>
+      <c r="AL100" s="16"/>
+      <c r="AM100" s="16"/>
+      <c r="AN100" s="16"/>
+      <c r="AO100" s="16"/>
+      <c r="AP100" s="16"/>
+      <c r="AQ100" s="16"/>
+      <c r="AR100" s="16"/>
+      <c r="AS100" s="16"/>
+      <c r="AT100" s="16"/>
+      <c r="AU100" s="16"/>
+      <c r="AV100" s="16"/>
+      <c r="AZ100" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -19411,38 +19411,38 @@
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C118" s="9"/>
-      <c r="D118" s="9"/>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9"/>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
-      <c r="I118" s="9"/>
-      <c r="J118" s="9"/>
-      <c r="K118" s="9"/>
-      <c r="L118" s="9"/>
-      <c r="M118" s="9"/>
-      <c r="N118" s="9"/>
-      <c r="O118" s="9"/>
-      <c r="P118" s="9"/>
-      <c r="Q118" s="9"/>
-      <c r="R118" s="9"/>
-      <c r="S118" s="9"/>
-      <c r="T118" s="9"/>
-      <c r="U118" s="9"/>
-      <c r="V118" s="9"/>
-      <c r="W118" s="9"/>
-      <c r="X118" s="9"/>
-      <c r="Y118" s="9"/>
-      <c r="Z118" s="9"/>
-      <c r="AA118" s="9"/>
-      <c r="AB118" s="9"/>
-      <c r="AC118" s="9"/>
-      <c r="AD118" s="9"/>
-      <c r="AE118" s="9"/>
+      <c r="C118" s="16"/>
+      <c r="D118" s="16"/>
+      <c r="E118" s="16"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="16"/>
+      <c r="H118" s="16"/>
+      <c r="I118" s="16"/>
+      <c r="J118" s="16"/>
+      <c r="K118" s="16"/>
+      <c r="L118" s="16"/>
+      <c r="M118" s="16"/>
+      <c r="N118" s="16"/>
+      <c r="O118" s="16"/>
+      <c r="P118" s="16"/>
+      <c r="Q118" s="16"/>
+      <c r="R118" s="16"/>
+      <c r="S118" s="16"/>
+      <c r="T118" s="16"/>
+      <c r="U118" s="16"/>
+      <c r="V118" s="16"/>
+      <c r="W118" s="16"/>
+      <c r="X118" s="16"/>
+      <c r="Y118" s="16"/>
+      <c r="Z118" s="16"/>
+      <c r="AA118" s="16"/>
+      <c r="AB118" s="16"/>
+      <c r="AC118" s="16"/>
+      <c r="AD118" s="16"/>
+      <c r="AE118" s="16"/>
     </row>
     <row r="121" spans="1:31" ht="185" x14ac:dyDescent="0.2">
       <c r="B121" s="3" t="s">
@@ -21437,38 +21437,38 @@
       </c>
     </row>
     <row r="142" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C142" s="9"/>
-      <c r="D142" s="9"/>
-      <c r="E142" s="9"/>
-      <c r="F142" s="9"/>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
-      <c r="I142" s="9"/>
-      <c r="J142" s="9"/>
-      <c r="K142" s="9"/>
-      <c r="L142" s="9"/>
-      <c r="M142" s="9"/>
-      <c r="N142" s="9"/>
-      <c r="O142" s="9"/>
-      <c r="P142" s="9"/>
-      <c r="Q142" s="9"/>
-      <c r="R142" s="9"/>
-      <c r="S142" s="9"/>
-      <c r="T142" s="9"/>
-      <c r="U142" s="9"/>
-      <c r="V142" s="9"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="9"/>
-      <c r="Y142" s="9"/>
-      <c r="Z142" s="9"/>
-      <c r="AA142" s="9"/>
-      <c r="AB142" s="9"/>
-      <c r="AC142" s="9"/>
-      <c r="AD142" s="9"/>
-      <c r="AE142" s="9"/>
+      <c r="C142" s="16"/>
+      <c r="D142" s="16"/>
+      <c r="E142" s="16"/>
+      <c r="F142" s="16"/>
+      <c r="G142" s="16"/>
+      <c r="H142" s="16"/>
+      <c r="I142" s="16"/>
+      <c r="J142" s="16"/>
+      <c r="K142" s="16"/>
+      <c r="L142" s="16"/>
+      <c r="M142" s="16"/>
+      <c r="N142" s="16"/>
+      <c r="O142" s="16"/>
+      <c r="P142" s="16"/>
+      <c r="Q142" s="16"/>
+      <c r="R142" s="16"/>
+      <c r="S142" s="16"/>
+      <c r="T142" s="16"/>
+      <c r="U142" s="16"/>
+      <c r="V142" s="16"/>
+      <c r="W142" s="16"/>
+      <c r="X142" s="16"/>
+      <c r="Y142" s="16"/>
+      <c r="Z142" s="16"/>
+      <c r="AA142" s="16"/>
+      <c r="AB142" s="16"/>
+      <c r="AC142" s="16"/>
+      <c r="AD142" s="16"/>
+      <c r="AE142" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -21497,17 +21497,22 @@
     <col min="3" max="3" width="9.1640625" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="22" width="9.1640625" customWidth="1"/>
-    <col min="23" max="25" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="39" width="9.1640625" customWidth="1"/>
-    <col min="40" max="40" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="11.6640625" customWidth="1"/>
     <col min="42" max="44" width="9.1640625" customWidth="1"/>
     <col min="45" max="62" width="9" customWidth="1"/>
-    <col min="63" max="63" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="66" max="66" width="49.6640625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="68" max="74" width="9" bestFit="1" customWidth="1"/>
+    <col min="75" max="75" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="76" max="95" width="9" bestFit="1" customWidth="1"/>
     <col min="98" max="98" width="49.6640625" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="9" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:127" ht="179" x14ac:dyDescent="0.2">
@@ -33352,68 +33357,68 @@
       <c r="B64" s="5">
         <v>1</v>
       </c>
-      <c r="BO64" s="8" t="s">
+      <c r="BO64" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="BP64" s="9"/>
-      <c r="BQ64" s="9"/>
-      <c r="BR64" s="9"/>
-      <c r="BS64" s="9"/>
-      <c r="BT64" s="9"/>
-      <c r="BU64" s="9"/>
-      <c r="BV64" s="9"/>
-      <c r="BW64" s="9"/>
-      <c r="BX64" s="9"/>
-      <c r="BY64" s="9"/>
-      <c r="BZ64" s="9"/>
-      <c r="CA64" s="9"/>
-      <c r="CB64" s="9"/>
-      <c r="CC64" s="9"/>
-      <c r="CD64" s="9"/>
-      <c r="CE64" s="9"/>
-      <c r="CF64" s="9"/>
-      <c r="CG64" s="9"/>
-      <c r="CH64" s="9"/>
-      <c r="CI64" s="9"/>
-      <c r="CJ64" s="9"/>
-      <c r="CK64" s="9"/>
-      <c r="CL64" s="9"/>
-      <c r="CM64" s="9"/>
-      <c r="CN64" s="9"/>
-      <c r="CO64" s="9"/>
-      <c r="CP64" s="9"/>
-      <c r="CQ64" s="9"/>
-      <c r="CU64" s="8" t="s">
+      <c r="BP64" s="16"/>
+      <c r="BQ64" s="16"/>
+      <c r="BR64" s="16"/>
+      <c r="BS64" s="16"/>
+      <c r="BT64" s="16"/>
+      <c r="BU64" s="16"/>
+      <c r="BV64" s="16"/>
+      <c r="BW64" s="16"/>
+      <c r="BX64" s="16"/>
+      <c r="BY64" s="16"/>
+      <c r="BZ64" s="16"/>
+      <c r="CA64" s="16"/>
+      <c r="CB64" s="16"/>
+      <c r="CC64" s="16"/>
+      <c r="CD64" s="16"/>
+      <c r="CE64" s="16"/>
+      <c r="CF64" s="16"/>
+      <c r="CG64" s="16"/>
+      <c r="CH64" s="16"/>
+      <c r="CI64" s="16"/>
+      <c r="CJ64" s="16"/>
+      <c r="CK64" s="16"/>
+      <c r="CL64" s="16"/>
+      <c r="CM64" s="16"/>
+      <c r="CN64" s="16"/>
+      <c r="CO64" s="16"/>
+      <c r="CP64" s="16"/>
+      <c r="CQ64" s="16"/>
+      <c r="CU64" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="CV64" s="9"/>
-      <c r="CW64" s="9"/>
-      <c r="CX64" s="9"/>
-      <c r="CY64" s="9"/>
-      <c r="CZ64" s="9"/>
-      <c r="DA64" s="9"/>
-      <c r="DB64" s="9"/>
-      <c r="DC64" s="9"/>
-      <c r="DD64" s="9"/>
-      <c r="DE64" s="9"/>
-      <c r="DF64" s="9"/>
-      <c r="DG64" s="9"/>
-      <c r="DH64" s="9"/>
-      <c r="DI64" s="9"/>
-      <c r="DJ64" s="9"/>
-      <c r="DK64" s="9"/>
-      <c r="DL64" s="9"/>
-      <c r="DM64" s="9"/>
-      <c r="DN64" s="9"/>
-      <c r="DO64" s="9"/>
-      <c r="DP64" s="9"/>
-      <c r="DQ64" s="9"/>
-      <c r="DR64" s="9"/>
-      <c r="DS64" s="9"/>
-      <c r="DT64" s="9"/>
-      <c r="DU64" s="9"/>
-      <c r="DV64" s="9"/>
-      <c r="DW64" s="9"/>
+      <c r="CV64" s="16"/>
+      <c r="CW64" s="16"/>
+      <c r="CX64" s="16"/>
+      <c r="CY64" s="16"/>
+      <c r="CZ64" s="16"/>
+      <c r="DA64" s="16"/>
+      <c r="DB64" s="16"/>
+      <c r="DC64" s="16"/>
+      <c r="DD64" s="16"/>
+      <c r="DE64" s="16"/>
+      <c r="DF64" s="16"/>
+      <c r="DG64" s="16"/>
+      <c r="DH64" s="16"/>
+      <c r="DI64" s="16"/>
+      <c r="DJ64" s="16"/>
+      <c r="DK64" s="16"/>
+      <c r="DL64" s="16"/>
+      <c r="DM64" s="16"/>
+      <c r="DN64" s="16"/>
+      <c r="DO64" s="16"/>
+      <c r="DP64" s="16"/>
+      <c r="DQ64" s="16"/>
+      <c r="DR64" s="16"/>
+      <c r="DS64" s="16"/>
+      <c r="DT64" s="16"/>
+      <c r="DU64" s="16"/>
+      <c r="DV64" s="16"/>
+      <c r="DW64" s="16"/>
     </row>
     <row r="65" spans="1:95" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
@@ -34899,7 +34904,7 @@
       </c>
     </row>
     <row r="82" spans="1:95" x14ac:dyDescent="0.2">
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="15" t="s">
         <v>53</v>
       </c>
       <c r="BN82" s="2" t="s">
@@ -39318,37 +39323,37 @@
       </c>
     </row>
     <row r="130" spans="66:100" x14ac:dyDescent="0.2">
-      <c r="BO130" s="8" t="s">
+      <c r="BO130" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="BP130" s="9"/>
-      <c r="BQ130" s="9"/>
-      <c r="BR130" s="9"/>
-      <c r="BS130" s="9"/>
-      <c r="BT130" s="9"/>
-      <c r="BU130" s="9"/>
-      <c r="BV130" s="9"/>
-      <c r="BW130" s="9"/>
-      <c r="BX130" s="9"/>
-      <c r="BY130" s="9"/>
-      <c r="BZ130" s="9"/>
-      <c r="CA130" s="9"/>
-      <c r="CB130" s="9"/>
-      <c r="CC130" s="9"/>
-      <c r="CD130" s="9"/>
-      <c r="CE130" s="9"/>
-      <c r="CF130" s="9"/>
-      <c r="CG130" s="9"/>
-      <c r="CH130" s="9"/>
-      <c r="CI130" s="9"/>
-      <c r="CJ130" s="9"/>
-      <c r="CK130" s="9"/>
-      <c r="CL130" s="9"/>
-      <c r="CM130" s="9"/>
-      <c r="CN130" s="9"/>
-      <c r="CO130" s="9"/>
-      <c r="CP130" s="9"/>
-      <c r="CQ130" s="9"/>
+      <c r="BP130" s="16"/>
+      <c r="BQ130" s="16"/>
+      <c r="BR130" s="16"/>
+      <c r="BS130" s="16"/>
+      <c r="BT130" s="16"/>
+      <c r="BU130" s="16"/>
+      <c r="BV130" s="16"/>
+      <c r="BW130" s="16"/>
+      <c r="BX130" s="16"/>
+      <c r="BY130" s="16"/>
+      <c r="BZ130" s="16"/>
+      <c r="CA130" s="16"/>
+      <c r="CB130" s="16"/>
+      <c r="CC130" s="16"/>
+      <c r="CD130" s="16"/>
+      <c r="CE130" s="16"/>
+      <c r="CF130" s="16"/>
+      <c r="CG130" s="16"/>
+      <c r="CH130" s="16"/>
+      <c r="CI130" s="16"/>
+      <c r="CJ130" s="16"/>
+      <c r="CK130" s="16"/>
+      <c r="CL130" s="16"/>
+      <c r="CM130" s="16"/>
+      <c r="CN130" s="16"/>
+      <c r="CO130" s="16"/>
+      <c r="CP130" s="16"/>
+      <c r="CQ130" s="16"/>
     </row>
     <row r="133" spans="66:100" ht="179" x14ac:dyDescent="0.2">
       <c r="BO133" s="3" t="s">
@@ -45708,41 +45713,41 @@
       </c>
     </row>
     <row r="196" spans="1:100" x14ac:dyDescent="0.2">
-      <c r="BO196" s="8" t="s">
+      <c r="BO196" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="BP196" s="9"/>
-      <c r="BQ196" s="9"/>
-      <c r="BR196" s="9"/>
-      <c r="BS196" s="9"/>
-      <c r="BT196" s="9"/>
-      <c r="BU196" s="9"/>
-      <c r="BV196" s="9"/>
-      <c r="BW196" s="9"/>
-      <c r="BX196" s="9"/>
-      <c r="BY196" s="9"/>
-      <c r="BZ196" s="9"/>
-      <c r="CA196" s="9"/>
-      <c r="CB196" s="9"/>
-      <c r="CC196" s="9"/>
-      <c r="CD196" s="9"/>
-      <c r="CE196" s="9"/>
-      <c r="CF196" s="9"/>
-      <c r="CG196" s="9"/>
-      <c r="CH196" s="9"/>
-      <c r="CI196" s="9"/>
-      <c r="CJ196" s="9"/>
-      <c r="CK196" s="9"/>
-      <c r="CL196" s="9"/>
-      <c r="CM196" s="9"/>
-      <c r="CN196" s="9"/>
-      <c r="CO196" s="9"/>
-      <c r="CP196" s="9"/>
-      <c r="CQ196" s="9"/>
-      <c r="CU196" s="8" t="s">
+      <c r="BP196" s="16"/>
+      <c r="BQ196" s="16"/>
+      <c r="BR196" s="16"/>
+      <c r="BS196" s="16"/>
+      <c r="BT196" s="16"/>
+      <c r="BU196" s="16"/>
+      <c r="BV196" s="16"/>
+      <c r="BW196" s="16"/>
+      <c r="BX196" s="16"/>
+      <c r="BY196" s="16"/>
+      <c r="BZ196" s="16"/>
+      <c r="CA196" s="16"/>
+      <c r="CB196" s="16"/>
+      <c r="CC196" s="16"/>
+      <c r="CD196" s="16"/>
+      <c r="CE196" s="16"/>
+      <c r="CF196" s="16"/>
+      <c r="CG196" s="16"/>
+      <c r="CH196" s="16"/>
+      <c r="CI196" s="16"/>
+      <c r="CJ196" s="16"/>
+      <c r="CK196" s="16"/>
+      <c r="CL196" s="16"/>
+      <c r="CM196" s="16"/>
+      <c r="CN196" s="16"/>
+      <c r="CO196" s="16"/>
+      <c r="CP196" s="16"/>
+      <c r="CQ196" s="16"/>
+      <c r="CU196" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="CV196" s="9"/>
+      <c r="CV196" s="16"/>
     </row>
     <row r="197" spans="1:100" x14ac:dyDescent="0.2">
       <c r="BO197" s="6">
@@ -51706,70 +51711,70 @@
       </c>
     </row>
     <row r="229" spans="1:64" x14ac:dyDescent="0.2">
-      <c r="B229" s="8" t="s">
+      <c r="B229" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
-      <c r="E229" s="9"/>
-      <c r="F229" s="9"/>
-      <c r="G229" s="9"/>
-      <c r="H229" s="9"/>
-      <c r="I229" s="9"/>
-      <c r="J229" s="9"/>
-      <c r="K229" s="9"/>
-      <c r="L229" s="9"/>
-      <c r="M229" s="9"/>
-      <c r="N229" s="9"/>
-      <c r="O229" s="9"/>
-      <c r="P229" s="9"/>
-      <c r="Q229" s="9"/>
-      <c r="R229" s="9"/>
-      <c r="S229" s="9"/>
-      <c r="T229" s="9"/>
-      <c r="U229" s="9"/>
-      <c r="V229" s="9"/>
-      <c r="W229" s="9"/>
-      <c r="X229" s="9"/>
-      <c r="Y229" s="9"/>
-      <c r="Z229" s="9"/>
-      <c r="AA229" s="9"/>
-      <c r="AB229" s="9"/>
-      <c r="AC229" s="9"/>
-      <c r="AD229" s="9"/>
-      <c r="AE229" s="9"/>
-      <c r="AF229" s="9"/>
-      <c r="AG229" s="9"/>
-      <c r="AH229" s="9"/>
-      <c r="AI229" s="9"/>
-      <c r="AJ229" s="9"/>
-      <c r="AK229" s="9"/>
-      <c r="AL229" s="9"/>
-      <c r="AM229" s="9"/>
-      <c r="AN229" s="9"/>
-      <c r="AO229" s="9"/>
-      <c r="AP229" s="9"/>
-      <c r="AQ229" s="9"/>
-      <c r="AR229" s="9"/>
-      <c r="AS229" s="9"/>
-      <c r="AT229" s="9"/>
-      <c r="AU229" s="9"/>
-      <c r="AV229" s="9"/>
-      <c r="AW229" s="9"/>
-      <c r="AX229" s="9"/>
-      <c r="AY229" s="9"/>
-      <c r="AZ229" s="9"/>
-      <c r="BA229" s="9"/>
-      <c r="BB229" s="9"/>
-      <c r="BC229" s="9"/>
-      <c r="BD229" s="9"/>
-      <c r="BE229" s="9"/>
-      <c r="BF229" s="9"/>
-      <c r="BG229" s="9"/>
-      <c r="BH229" s="9"/>
-      <c r="BI229" s="9"/>
-      <c r="BJ229" s="9"/>
-      <c r="BK229" s="9"/>
+      <c r="C229" s="16"/>
+      <c r="D229" s="16"/>
+      <c r="E229" s="16"/>
+      <c r="F229" s="16"/>
+      <c r="G229" s="16"/>
+      <c r="H229" s="16"/>
+      <c r="I229" s="16"/>
+      <c r="J229" s="16"/>
+      <c r="K229" s="16"/>
+      <c r="L229" s="16"/>
+      <c r="M229" s="16"/>
+      <c r="N229" s="16"/>
+      <c r="O229" s="16"/>
+      <c r="P229" s="16"/>
+      <c r="Q229" s="16"/>
+      <c r="R229" s="16"/>
+      <c r="S229" s="16"/>
+      <c r="T229" s="16"/>
+      <c r="U229" s="16"/>
+      <c r="V229" s="16"/>
+      <c r="W229" s="16"/>
+      <c r="X229" s="16"/>
+      <c r="Y229" s="16"/>
+      <c r="Z229" s="16"/>
+      <c r="AA229" s="16"/>
+      <c r="AB229" s="16"/>
+      <c r="AC229" s="16"/>
+      <c r="AD229" s="16"/>
+      <c r="AE229" s="16"/>
+      <c r="AF229" s="16"/>
+      <c r="AG229" s="16"/>
+      <c r="AH229" s="16"/>
+      <c r="AI229" s="16"/>
+      <c r="AJ229" s="16"/>
+      <c r="AK229" s="16"/>
+      <c r="AL229" s="16"/>
+      <c r="AM229" s="16"/>
+      <c r="AN229" s="16"/>
+      <c r="AO229" s="16"/>
+      <c r="AP229" s="16"/>
+      <c r="AQ229" s="16"/>
+      <c r="AR229" s="16"/>
+      <c r="AS229" s="16"/>
+      <c r="AT229" s="16"/>
+      <c r="AU229" s="16"/>
+      <c r="AV229" s="16"/>
+      <c r="AW229" s="16"/>
+      <c r="AX229" s="16"/>
+      <c r="AY229" s="16"/>
+      <c r="AZ229" s="16"/>
+      <c r="BA229" s="16"/>
+      <c r="BB229" s="16"/>
+      <c r="BC229" s="16"/>
+      <c r="BD229" s="16"/>
+      <c r="BE229" s="16"/>
+      <c r="BF229" s="16"/>
+      <c r="BG229" s="16"/>
+      <c r="BH229" s="16"/>
+      <c r="BI229" s="16"/>
+      <c r="BJ229" s="16"/>
+      <c r="BK229" s="16"/>
     </row>
     <row r="232" spans="1:64" ht="236" x14ac:dyDescent="0.2">
       <c r="B232" s="3" t="s">
@@ -56544,89 +56549,89 @@
       </c>
     </row>
     <row r="257" spans="1:63" x14ac:dyDescent="0.2">
-      <c r="B257" s="8" t="s">
+      <c r="B257" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
-      <c r="E257" s="9"/>
-      <c r="F257" s="9"/>
-      <c r="G257" s="9"/>
-      <c r="H257" s="9"/>
-      <c r="I257" s="9"/>
-      <c r="J257" s="9"/>
-      <c r="K257" s="9"/>
-      <c r="L257" s="9"/>
-      <c r="M257" s="9"/>
-      <c r="N257" s="9"/>
-      <c r="O257" s="9"/>
-      <c r="P257" s="9"/>
-      <c r="Q257" s="9"/>
-      <c r="R257" s="9"/>
-      <c r="S257" s="9"/>
-      <c r="T257" s="9"/>
-      <c r="U257" s="9"/>
-      <c r="V257" s="9"/>
-      <c r="W257" s="9"/>
-      <c r="X257" s="9"/>
-      <c r="Y257" s="9"/>
-      <c r="Z257" s="9"/>
-      <c r="AA257" s="9"/>
-      <c r="AB257" s="9"/>
-      <c r="AC257" s="9"/>
-      <c r="AD257" s="9"/>
-      <c r="AE257" s="9"/>
-      <c r="AF257" s="9"/>
-      <c r="AG257" s="9"/>
-      <c r="AH257" s="9"/>
-      <c r="AI257" s="9"/>
-      <c r="AJ257" s="9"/>
-      <c r="AK257" s="9"/>
-      <c r="AL257" s="9"/>
-      <c r="AM257" s="9"/>
-      <c r="AN257" s="9"/>
-      <c r="AO257" s="9"/>
-      <c r="AP257" s="9"/>
-      <c r="AQ257" s="9"/>
-      <c r="AR257" s="9"/>
-      <c r="AS257" s="9"/>
-      <c r="AT257" s="9"/>
-      <c r="AU257" s="9"/>
-      <c r="AV257" s="9"/>
-      <c r="AW257" s="9"/>
-      <c r="AX257" s="9"/>
-      <c r="AY257" s="9"/>
-      <c r="AZ257" s="9"/>
-      <c r="BA257" s="9"/>
-      <c r="BB257" s="9"/>
-      <c r="BC257" s="9"/>
-      <c r="BD257" s="9"/>
-      <c r="BE257" s="9"/>
-      <c r="BF257" s="9"/>
-      <c r="BG257" s="9"/>
-      <c r="BH257" s="9"/>
-      <c r="BI257" s="9"/>
-      <c r="BJ257" s="9"/>
-      <c r="BK257" s="9"/>
+      <c r="C257" s="16"/>
+      <c r="D257" s="16"/>
+      <c r="E257" s="16"/>
+      <c r="F257" s="16"/>
+      <c r="G257" s="16"/>
+      <c r="H257" s="16"/>
+      <c r="I257" s="16"/>
+      <c r="J257" s="16"/>
+      <c r="K257" s="16"/>
+      <c r="L257" s="16"/>
+      <c r="M257" s="16"/>
+      <c r="N257" s="16"/>
+      <c r="O257" s="16"/>
+      <c r="P257" s="16"/>
+      <c r="Q257" s="16"/>
+      <c r="R257" s="16"/>
+      <c r="S257" s="16"/>
+      <c r="T257" s="16"/>
+      <c r="U257" s="16"/>
+      <c r="V257" s="16"/>
+      <c r="W257" s="16"/>
+      <c r="X257" s="16"/>
+      <c r="Y257" s="16"/>
+      <c r="Z257" s="16"/>
+      <c r="AA257" s="16"/>
+      <c r="AB257" s="16"/>
+      <c r="AC257" s="16"/>
+      <c r="AD257" s="16"/>
+      <c r="AE257" s="16"/>
+      <c r="AF257" s="16"/>
+      <c r="AG257" s="16"/>
+      <c r="AH257" s="16"/>
+      <c r="AI257" s="16"/>
+      <c r="AJ257" s="16"/>
+      <c r="AK257" s="16"/>
+      <c r="AL257" s="16"/>
+      <c r="AM257" s="16"/>
+      <c r="AN257" s="16"/>
+      <c r="AO257" s="16"/>
+      <c r="AP257" s="16"/>
+      <c r="AQ257" s="16"/>
+      <c r="AR257" s="16"/>
+      <c r="AS257" s="16"/>
+      <c r="AT257" s="16"/>
+      <c r="AU257" s="16"/>
+      <c r="AV257" s="16"/>
+      <c r="AW257" s="16"/>
+      <c r="AX257" s="16"/>
+      <c r="AY257" s="16"/>
+      <c r="AZ257" s="16"/>
+      <c r="BA257" s="16"/>
+      <c r="BB257" s="16"/>
+      <c r="BC257" s="16"/>
+      <c r="BD257" s="16"/>
+      <c r="BE257" s="16"/>
+      <c r="BF257" s="16"/>
+      <c r="BG257" s="16"/>
+      <c r="BH257" s="16"/>
+      <c r="BI257" s="16"/>
+      <c r="BJ257" s="16"/>
+      <c r="BK257" s="16"/>
     </row>
     <row r="267" spans="1:63" x14ac:dyDescent="0.2">
       <c r="A267" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B267" s="10">
+      <c r="B267" s="8">
         <f>BL200</f>
         <v>12901300.755606335</v>
       </c>
-      <c r="C267" s="14"/>
-      <c r="D267" s="10" cm="1">
+      <c r="C267" s="12"/>
+      <c r="D267" s="8" cm="1">
         <f t="array" ref="D267:D295">TRANSPOSE(BO197:CQ197)</f>
         <v>12203629.286624292</v>
       </c>
-      <c r="F267" s="13">
+      <c r="F267" s="11">
         <f>B267/D267 * 100</f>
         <v>105.71691791512154</v>
       </c>
-      <c r="H267" s="11">
+      <c r="H267" s="9">
         <f>D267-B267</f>
         <v>-697671.46898204274</v>
       </c>
@@ -56635,19 +56640,19 @@
       <c r="A268" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B268" s="10">
+      <c r="B268" s="8">
         <f t="shared" ref="B268:B295" si="2">BL201</f>
         <v>8855801.2791533191</v>
       </c>
-      <c r="C268" s="14"/>
-      <c r="D268" s="10">
+      <c r="C268" s="12"/>
+      <c r="D268" s="8">
         <v>8855851.6372374725</v>
       </c>
-      <c r="F268" s="16">
+      <c r="F268" s="14">
         <f t="shared" ref="F268:F295" si="3">B268/D268 * 100</f>
         <v>99.999431358087094</v>
       </c>
-      <c r="H268" s="12">
+      <c r="H268" s="10">
         <f t="shared" ref="H268:H295" si="4">D268-B268</f>
         <v>50.35808415338397</v>
       </c>
@@ -56656,19 +56661,19 @@
       <c r="A269" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B269" s="10">
+      <c r="B269" s="8">
         <f t="shared" si="2"/>
         <v>8866059.6630040724</v>
       </c>
-      <c r="C269" s="14"/>
-      <c r="D269" s="10">
+      <c r="C269" s="12"/>
+      <c r="D269" s="8">
         <v>8954947.1516316663</v>
       </c>
-      <c r="F269" s="16">
+      <c r="F269" s="14">
         <f t="shared" si="3"/>
         <v>99.007392370692017</v>
       </c>
-      <c r="H269" s="12">
+      <c r="H269" s="10">
         <f t="shared" si="4"/>
         <v>88887.488627593964</v>
       </c>
@@ -56677,19 +56682,19 @@
       <c r="A270" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B270" s="10">
+      <c r="B270" s="8">
         <f t="shared" si="2"/>
         <v>8855801.2791533191</v>
       </c>
-      <c r="C270" s="14"/>
-      <c r="D270" s="10">
+      <c r="C270" s="12"/>
+      <c r="D270" s="8">
         <v>8856083.4079243504</v>
       </c>
-      <c r="F270" s="16">
+      <c r="F270" s="14">
         <f t="shared" si="3"/>
         <v>99.996814294106812</v>
       </c>
-      <c r="H270" s="12">
+      <c r="H270" s="10">
         <f t="shared" si="4"/>
         <v>282.12877103127539</v>
       </c>
@@ -56698,19 +56703,19 @@
       <c r="A271" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B271" s="10">
+      <c r="B271" s="8">
         <f t="shared" si="2"/>
         <v>53172.707333649501</v>
       </c>
-      <c r="C271" s="14"/>
-      <c r="D271" s="10">
+      <c r="C271" s="12"/>
+      <c r="D271" s="8">
         <v>80113.817233019901</v>
       </c>
-      <c r="F271" s="16">
+      <c r="F271" s="14">
         <f t="shared" si="3"/>
         <v>66.371456472971204</v>
       </c>
-      <c r="H271" s="12">
+      <c r="H271" s="10">
         <f t="shared" si="4"/>
         <v>26941.1098993704</v>
       </c>
@@ -56719,19 +56724,19 @@
       <c r="A272" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B272" s="10">
+      <c r="B272" s="8">
         <f t="shared" si="2"/>
         <v>3207199.0568874623</v>
       </c>
-      <c r="C272" s="14"/>
-      <c r="D272" s="10">
+      <c r="C272" s="12"/>
+      <c r="D272" s="8">
         <v>3207824.8619438512</v>
       </c>
-      <c r="F272" s="16">
+      <c r="F272" s="14">
         <f t="shared" si="3"/>
         <v>99.980491296023871</v>
       </c>
-      <c r="H272" s="12">
+      <c r="H272" s="10">
         <f t="shared" si="4"/>
         <v>625.80505638895556</v>
       </c>
@@ -56740,19 +56745,19 @@
       <c r="A273" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B273" s="10">
+      <c r="B273" s="8">
         <f t="shared" si="2"/>
         <v>4043362.1745084701</v>
       </c>
-      <c r="C273" s="14"/>
-      <c r="D273" s="10">
+      <c r="C273" s="12"/>
+      <c r="D273" s="8">
         <v>4043362.1745084701</v>
       </c>
-      <c r="F273" s="16">
+      <c r="F273" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H273" s="12">
+      <c r="H273" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -56761,19 +56766,19 @@
       <c r="A274" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B274" s="10">
+      <c r="B274" s="8">
         <f t="shared" si="2"/>
         <v>4062085.6955903294</v>
       </c>
-      <c r="C274" s="14"/>
-      <c r="D274" s="10">
+      <c r="C274" s="12"/>
+      <c r="D274" s="8">
         <v>4059364.8846815075</v>
       </c>
-      <c r="F274" s="13">
+      <c r="F274" s="11">
         <f t="shared" si="3"/>
         <v>100.06702553197641</v>
       </c>
-      <c r="H274" s="11">
+      <c r="H274" s="9">
         <f t="shared" si="4"/>
         <v>-2720.8109088218771</v>
       </c>
@@ -56782,19 +56787,19 @@
       <c r="A275" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B275" s="10">
+      <c r="B275" s="8">
         <f t="shared" si="2"/>
         <v>23470360.302962191</v>
       </c>
-      <c r="C275" s="14"/>
-      <c r="D275" s="10">
+      <c r="C275" s="12"/>
+      <c r="D275" s="8">
         <v>19453994.354444001</v>
       </c>
-      <c r="F275" s="13">
+      <c r="F275" s="11">
         <f t="shared" si="3"/>
         <v>120.64545653371543</v>
       </c>
-      <c r="H275" s="11">
+      <c r="H275" s="9">
         <f t="shared" si="4"/>
         <v>-4016365.9485181905</v>
       </c>
@@ -56803,19 +56808,19 @@
       <c r="A276" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B276" s="10">
+      <c r="B276" s="8">
         <f t="shared" si="2"/>
         <v>8815.93173696554</v>
       </c>
-      <c r="C276" s="14"/>
-      <c r="D276" s="10">
+      <c r="C276" s="12"/>
+      <c r="D276" s="8">
         <v>10407.5335702298</v>
       </c>
-      <c r="F276" s="16">
+      <c r="F276" s="14">
         <f t="shared" si="3"/>
         <v>84.707214033717335</v>
       </c>
-      <c r="H276" s="12">
+      <c r="H276" s="10">
         <f t="shared" si="4"/>
         <v>1591.6018332642598</v>
       </c>
@@ -56824,19 +56829,19 @@
       <c r="A277" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B277" s="10">
+      <c r="B277" s="8">
         <f t="shared" si="2"/>
         <v>119815.67280747239</v>
       </c>
-      <c r="C277" s="14"/>
-      <c r="D277" s="10">
+      <c r="C277" s="12"/>
+      <c r="D277" s="8">
         <v>120804.62739477069</v>
       </c>
-      <c r="F277" s="16">
+      <c r="F277" s="14">
         <f t="shared" si="3"/>
         <v>99.181360343038392</v>
       </c>
-      <c r="H277" s="12">
+      <c r="H277" s="10">
         <f t="shared" si="4"/>
         <v>988.95458729829988</v>
       </c>
@@ -56845,19 +56850,19 @@
       <c r="A278" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B278" s="10">
+      <c r="B278" s="8">
         <f t="shared" si="2"/>
         <v>131828.26141586457</v>
       </c>
-      <c r="C278" s="14"/>
-      <c r="D278" s="10">
+      <c r="C278" s="12"/>
+      <c r="D278" s="8">
         <v>202449.0921090013</v>
       </c>
-      <c r="F278" s="16">
+      <c r="F278" s="14">
         <f t="shared" si="3"/>
         <v>65.116746161986484</v>
       </c>
-      <c r="H278" s="12">
+      <c r="H278" s="10">
         <f t="shared" si="4"/>
         <v>70620.830693136726</v>
       </c>
@@ -56866,19 +56871,19 @@
       <c r="A279" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B279" s="10">
+      <c r="B279" s="8">
         <f t="shared" si="2"/>
         <v>108178.528568432</v>
       </c>
-      <c r="C279" s="15"/>
-      <c r="D279" s="10">
+      <c r="C279" s="13"/>
+      <c r="D279" s="8">
         <v>717970.78032777994</v>
       </c>
-      <c r="F279" s="16">
+      <c r="F279" s="14">
         <f t="shared" si="3"/>
         <v>15.067260608996447</v>
       </c>
-      <c r="H279" s="12">
+      <c r="H279" s="10">
         <f t="shared" si="4"/>
         <v>609792.25175934797</v>
       </c>
@@ -56887,19 +56892,19 @@
       <c r="A280" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B280" s="10">
+      <c r="B280" s="8">
         <f t="shared" si="2"/>
         <v>25296.465222981598</v>
       </c>
-      <c r="C280" s="14"/>
-      <c r="D280" s="10">
+      <c r="C280" s="12"/>
+      <c r="D280" s="8">
         <v>25331.143318145714</v>
       </c>
-      <c r="F280" s="16">
+      <c r="F280" s="14">
         <f t="shared" si="3"/>
         <v>99.863100947602021</v>
       </c>
-      <c r="H280" s="12">
+      <c r="H280" s="10">
         <f t="shared" si="4"/>
         <v>34.678095164115803</v>
       </c>
@@ -56908,19 +56913,19 @@
       <c r="A281" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B281" s="10">
+      <c r="B281" s="8">
         <f t="shared" si="2"/>
         <v>25343.321287334067</v>
       </c>
-      <c r="C281" s="14"/>
-      <c r="D281" s="10">
+      <c r="C281" s="12"/>
+      <c r="D281" s="8">
         <v>25578.908283769375</v>
       </c>
-      <c r="F281" s="16">
+      <c r="F281" s="14">
         <f t="shared" si="3"/>
         <v>99.078979470813479</v>
       </c>
-      <c r="H281" s="12">
+      <c r="H281" s="10">
         <f t="shared" si="4"/>
         <v>235.58699643530781</v>
       </c>
@@ -56929,19 +56934,19 @@
       <c r="A282" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B282" s="10">
+      <c r="B282" s="8">
         <f t="shared" si="2"/>
         <v>25296.465222981598</v>
       </c>
-      <c r="C282" s="14"/>
-      <c r="D282" s="10">
+      <c r="C282" s="12"/>
+      <c r="D282" s="8">
         <v>28121.350870726517</v>
       </c>
-      <c r="F282" s="16">
+      <c r="F282" s="14">
         <f t="shared" si="3"/>
         <v>89.954658790287553</v>
       </c>
-      <c r="H282" s="12">
+      <c r="H282" s="10">
         <f t="shared" si="4"/>
         <v>2824.885647744919</v>
       </c>
@@ -56950,19 +56955,19 @@
       <c r="A283" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B283" s="10">
+      <c r="B283" s="8">
         <f t="shared" si="2"/>
         <v>1846413.5713607739</v>
       </c>
-      <c r="C283" s="14"/>
-      <c r="D283" s="10">
+      <c r="C283" s="12"/>
+      <c r="D283" s="8">
         <v>3284366.0335816354</v>
       </c>
-      <c r="F283" s="16">
+      <c r="F283" s="14">
         <f t="shared" si="3"/>
         <v>56.21826411799907</v>
       </c>
-      <c r="H283" s="12">
+      <c r="H283" s="10">
         <f t="shared" si="4"/>
         <v>1437952.4622208616</v>
       </c>
@@ -56971,19 +56976,19 @@
       <c r="A284" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B284" s="10">
+      <c r="B284" s="8">
         <f t="shared" si="2"/>
         <v>4830.4442158522497</v>
       </c>
-      <c r="C284" s="14"/>
-      <c r="D284" s="10">
+      <c r="C284" s="12"/>
+      <c r="D284" s="8">
         <v>4830.4442158522497</v>
       </c>
-      <c r="F284" s="16">
+      <c r="F284" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H284" s="12">
+      <c r="H284" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -56992,19 +56997,19 @@
       <c r="A285" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B285" s="10">
+      <c r="B285" s="8">
         <f t="shared" si="2"/>
         <v>184686.52821315001</v>
       </c>
-      <c r="C285" s="14"/>
-      <c r="D285" s="10">
+      <c r="C285" s="12"/>
+      <c r="D285" s="8">
         <v>184686.52821315001</v>
       </c>
-      <c r="F285" s="16">
+      <c r="F285" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H285" s="12">
+      <c r="H285" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57013,19 +57018,19 @@
       <c r="A286" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B286" s="10">
+      <c r="B286" s="8">
         <f t="shared" si="2"/>
         <v>5023.7890204088299</v>
       </c>
-      <c r="C286" s="14"/>
-      <c r="D286" s="10">
+      <c r="C286" s="12"/>
+      <c r="D286" s="8">
         <v>5023.7890204088299</v>
       </c>
-      <c r="F286" s="16">
+      <c r="F286" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H286" s="12">
+      <c r="H286" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57034,19 +57039,19 @@
       <c r="A287" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B287" s="10">
+      <c r="B287" s="8">
         <f t="shared" si="2"/>
         <v>82.091627997489695</v>
       </c>
-      <c r="C287" s="14"/>
-      <c r="D287" s="10">
+      <c r="C287" s="12"/>
+      <c r="D287" s="8">
         <v>82.091627997489695</v>
       </c>
-      <c r="F287" s="16">
+      <c r="F287" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H287" s="12">
+      <c r="H287" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57055,19 +57060,19 @@
       <c r="A288" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B288" s="10">
+      <c r="B288" s="8">
         <f t="shared" si="2"/>
         <v>43.206119998678503</v>
       </c>
-      <c r="C288" s="14"/>
-      <c r="D288" s="10">
+      <c r="C288" s="12"/>
+      <c r="D288" s="8">
         <v>43.206119998678503</v>
       </c>
-      <c r="F288" s="16">
+      <c r="F288" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H288" s="12">
+      <c r="H288" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57076,19 +57081,19 @@
       <c r="A289" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B289" s="10">
+      <c r="B289" s="8">
         <f t="shared" si="2"/>
         <v>6684024.7202526899</v>
       </c>
-      <c r="C289" s="14"/>
-      <c r="D289" s="10">
+      <c r="C289" s="12"/>
+      <c r="D289" s="8">
         <v>6738371.0065200189</v>
       </c>
-      <c r="F289" s="16">
+      <c r="F289" s="14">
         <f t="shared" si="3"/>
         <v>99.193480349853928</v>
       </c>
-      <c r="H289" s="12">
+      <c r="H289" s="10">
         <f t="shared" si="4"/>
         <v>54346.286267329007</v>
       </c>
@@ -57097,19 +57102,19 @@
       <c r="A290" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B290" s="10">
+      <c r="B290" s="8">
         <f t="shared" si="2"/>
         <v>3749358.36805565</v>
       </c>
-      <c r="C290" s="14"/>
-      <c r="D290" s="10">
+      <c r="C290" s="12"/>
+      <c r="D290" s="8">
         <v>3749358.36805565</v>
       </c>
-      <c r="F290" s="16">
+      <c r="F290" s="14">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="H290" s="12">
+      <c r="H290" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57118,19 +57123,19 @@
       <c r="A291" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B291" s="10">
+      <c r="B291" s="8">
         <f t="shared" si="2"/>
         <v>60946.554310340602</v>
       </c>
-      <c r="C291" s="14"/>
-      <c r="D291" s="10">
+      <c r="C291" s="12"/>
+      <c r="D291" s="8">
         <v>184686.52821315001</v>
       </c>
-      <c r="F291" s="16">
+      <c r="F291" s="14">
         <f t="shared" si="3"/>
         <v>33.000000000000597</v>
       </c>
-      <c r="H291" s="12">
+      <c r="H291" s="10">
         <f t="shared" si="4"/>
         <v>123739.9739028094</v>
       </c>
@@ -57139,19 +57144,19 @@
       <c r="A292" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B292" s="10">
+      <c r="B292" s="8">
         <f t="shared" si="2"/>
         <v>958.99457187397309</v>
       </c>
-      <c r="C292" s="14"/>
-      <c r="D292" s="10">
+      <c r="C292" s="12"/>
+      <c r="D292" s="8">
         <v>958.99457187397297</v>
       </c>
-      <c r="F292" s="16">
+      <c r="F292" s="14">
         <f t="shared" si="3"/>
         <v>100.00000000000003</v>
       </c>
-      <c r="H292" s="12">
+      <c r="H292" s="10">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
@@ -57160,19 +57165,19 @@
       <c r="A293" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B293" s="10">
+      <c r="B293" s="8">
         <f t="shared" si="2"/>
         <v>98905.719777386272</v>
       </c>
-      <c r="C293" s="14"/>
-      <c r="D293" s="10">
+      <c r="C293" s="12"/>
+      <c r="D293" s="8">
         <v>99968.352638963988</v>
       </c>
-      <c r="F293" s="16">
+      <c r="F293" s="14">
         <f t="shared" si="3"/>
         <v>98.937030736701828</v>
       </c>
-      <c r="H293" s="12">
+      <c r="H293" s="10">
         <f t="shared" si="4"/>
         <v>1062.6328615777165</v>
       </c>
@@ -57181,19 +57186,19 @@
       <c r="A294" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B294" s="10">
+      <c r="B294" s="8">
         <f t="shared" si="2"/>
         <v>1467038.1347699917</v>
       </c>
-      <c r="C294" s="14"/>
-      <c r="D294" s="10">
+      <c r="C294" s="12"/>
+      <c r="D294" s="8">
         <v>1979030.1382658123</v>
       </c>
-      <c r="F294" s="16">
+      <c r="F294" s="14">
         <f t="shared" si="3"/>
         <v>74.129145706468634</v>
       </c>
-      <c r="H294" s="12">
+      <c r="H294" s="10">
         <f t="shared" si="4"/>
         <v>511992.00349582057</v>
       </c>
@@ -57202,19 +57207,19 @@
       <c r="A295" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B295" s="10">
+      <c r="B295" s="8">
         <f t="shared" si="2"/>
         <v>23208.442077418957</v>
       </c>
-      <c r="C295" s="14"/>
-      <c r="D295" s="10">
+      <c r="C295" s="12"/>
+      <c r="D295" s="8">
         <v>21683.6909062671</v>
       </c>
-      <c r="F295" s="13">
+      <c r="F295" s="11">
         <f t="shared" si="3"/>
         <v>107.03178798177375</v>
       </c>
-      <c r="H295" s="11">
+      <c r="H295" s="9">
         <f t="shared" si="4"/>
         <v>-1524.7511711518564</v>
       </c>
